--- a/artfynd/Tyfallsjön artfynd.xlsx
+++ b/artfynd/Tyfallsjön artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY95"/>
+  <dimension ref="A1:AY99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67474872</v>
+        <v>67474646</v>
       </c>
       <c r="B2" t="n">
-        <v>92527</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>669710</v>
+        <v>668905</v>
       </c>
       <c r="R2" t="n">
-        <v>7090503</v>
+        <v>7090825</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>67474643</v>
+        <v>67474647</v>
       </c>
       <c r="B3" t="n">
-        <v>92527</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668901</v>
+        <v>668937</v>
       </c>
       <c r="R3" t="n">
-        <v>7090675</v>
+        <v>7090808</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67474648</v>
+        <v>67474651</v>
       </c>
       <c r="B4" t="n">
-        <v>78739</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668937</v>
+        <v>668977</v>
       </c>
       <c r="R4" t="n">
-        <v>7090808</v>
+        <v>7090760</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122745989</v>
+        <v>67474643</v>
       </c>
       <c r="B5" t="n">
-        <v>92527</v>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,14 +997,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ång</t>
+          <t>Stångsjömon, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>669893</v>
+        <v>668901</v>
       </c>
       <c r="R5" t="n">
-        <v>7090649</v>
+        <v>7090675</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1051,26 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Sören Uppsäll, Per Nihlén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122745991</v>
+        <v>67474644</v>
       </c>
       <c r="B6" t="n">
-        <v>92527</v>
+        <v>93191</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1078,34 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ång</t>
+          <t>Stångsjömon, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>669879</v>
+        <v>668905</v>
       </c>
       <c r="R6" t="n">
-        <v>7090606</v>
+        <v>7090679</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1132,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1152,26 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Sören Uppsäll, Per Nihlén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122745981</v>
+        <v>67474645</v>
       </c>
       <c r="B7" t="n">
-        <v>92527</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1179,34 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ång</t>
+          <t>Stångsjömon, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>670035</v>
+        <v>668922</v>
       </c>
       <c r="R7" t="n">
-        <v>7090545</v>
+        <v>7090748</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1233,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1253,26 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Sören Uppsäll, Per Nihlén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122745966</v>
+        <v>67474649</v>
       </c>
       <c r="B8" t="n">
-        <v>92527</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1280,34 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Storlandsberget N, Ång</t>
+          <t>Stångsjömon, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>670035</v>
+        <v>668949</v>
       </c>
       <c r="R8" t="n">
-        <v>7090454</v>
+        <v>7090807</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1334,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1354,48 +1342,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Sören Uppsäll, Per Nihlén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>67474874</v>
+        <v>67474650</v>
       </c>
       <c r="B9" t="n">
-        <v>78738</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>669648</v>
+        <v>668972</v>
       </c>
       <c r="R9" t="n">
-        <v>7090488</v>
+        <v>7090806</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>67474863</v>
+        <v>67474648</v>
       </c>
       <c r="B10" t="n">
-        <v>92551</v>
+        <v>79085</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>670109</v>
+        <v>668937</v>
       </c>
       <c r="R10" t="n">
-        <v>7089941</v>
+        <v>7090808</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122746094</v>
+        <v>67474657</v>
       </c>
       <c r="B11" t="n">
-        <v>91541</v>
+        <v>90932</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1575,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åskojan N, Ång</t>
+          <t>Stångsjömon, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>669736</v>
+        <v>669717</v>
       </c>
       <c r="R11" t="n">
-        <v>7090744</v>
+        <v>7090048</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1629,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1649,26 +1633,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Sören Uppsäll, Per Nihlén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122745975</v>
+        <v>67474877</v>
       </c>
       <c r="B12" t="n">
-        <v>92527</v>
+        <v>93191</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,34 +1656,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Ång</t>
+          <t>Stångsjömon, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>669892</v>
+        <v>669299</v>
       </c>
       <c r="R12" t="n">
-        <v>7090677</v>
+        <v>7090047</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1730,12 +1710,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1750,26 +1730,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Sören Uppsäll, Per Nihlén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122745959</v>
+        <v>67474654</v>
       </c>
       <c r="B13" t="n">
-        <v>92527</v>
+        <v>91930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1777,34 +1753,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ång</t>
+          <t>Stångsjömon, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>670125</v>
+        <v>669608</v>
       </c>
       <c r="R13" t="n">
-        <v>7090225</v>
+        <v>7090080</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1831,12 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1851,48 +1827,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Sören Uppsäll, Per Nihlén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>67474876</v>
+        <v>67474656</v>
       </c>
       <c r="B14" t="n">
-        <v>92547</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1902,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>669426</v>
+        <v>669722</v>
       </c>
       <c r="R14" t="n">
-        <v>7090382</v>
+        <v>7090036</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122746003</v>
+        <v>67474655</v>
       </c>
       <c r="B15" t="n">
-        <v>92563</v>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1975,34 +1947,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5449</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ång</t>
+          <t>Stångsjömon, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>669867</v>
+        <v>669647</v>
       </c>
       <c r="R15" t="n">
-        <v>7090564</v>
+        <v>7090068</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2029,12 +2001,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2049,26 +2021,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Sören Uppsäll, Per Nihlén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122743253</v>
+        <v>122743240</v>
       </c>
       <c r="B16" t="n">
-        <v>91265</v>
+        <v>78995</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2076,34 +2044,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gräningen SÖ, Ång</t>
+          <t>Gräningen Ö, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>669770</v>
+        <v>669806</v>
       </c>
       <c r="R16" t="n">
-        <v>7090696</v>
+        <v>7090755</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2155,21 +2123,21 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
+          <t>Jessica  Åström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>67474656</v>
+        <v>122743248</v>
       </c>
       <c r="B17" t="n">
-        <v>78980</v>
+        <v>92212</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2177,34 +2145,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stångsjömon, Ång</t>
+          <t>Gräningen Ö, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>669722</v>
+        <v>669743</v>
       </c>
       <c r="R17" t="n">
-        <v>7090036</v>
+        <v>7090749</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2231,12 +2199,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2251,57 +2219,61 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122745972</v>
+        <v>122746094</v>
       </c>
       <c r="B18" t="n">
-        <v>92539</v>
+        <v>92212</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4365</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Ång</t>
+          <t>Åskojan N, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>669935</v>
+        <v>669736</v>
       </c>
       <c r="R18" t="n">
-        <v>7090680</v>
+        <v>7090744</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2353,21 +2325,21 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
+          <t>Jessica  Åström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122745772</v>
+        <v>122746100</v>
       </c>
       <c r="B19" t="n">
-        <v>90283</v>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2375,34 +2347,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1962</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Ång</t>
+          <t>Åskojan SÖ, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>669892</v>
+        <v>669761</v>
       </c>
       <c r="R19" t="n">
-        <v>7090638</v>
+        <v>7090742</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2429,12 +2401,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2454,21 +2426,21 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Jessica  Åström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122745971</v>
+        <v>122743247</v>
       </c>
       <c r="B20" t="n">
-        <v>92727</v>
+        <v>91913</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2476,34 +2448,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2079</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Ång</t>
+          <t>Gräningen Ö, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>669936</v>
+        <v>669746</v>
       </c>
       <c r="R20" t="n">
-        <v>7090682</v>
+        <v>7090734</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2530,12 +2502,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2555,21 +2527,21 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
+          <t>Jessica  Åström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122745999</v>
+        <v>122746092</v>
       </c>
       <c r="B21" t="n">
-        <v>92727</v>
+        <v>91913</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2577,21 +2549,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2079</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2601,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>669873</v>
+        <v>669742</v>
       </c>
       <c r="R21" t="n">
-        <v>7090572</v>
+        <v>7090749</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2656,56 +2628,56 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
+          <t>Jessica  Åström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122745994</v>
+        <v>122743245</v>
       </c>
       <c r="B22" t="n">
-        <v>92535</v>
+        <v>92373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ång</t>
+          <t>Gräningen Ö, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>669879</v>
+        <v>669764</v>
       </c>
       <c r="R22" t="n">
-        <v>7090603</v>
+        <v>7090736</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2732,12 +2704,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2757,56 +2729,56 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
+          <t>Jessica  Åström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>67474646</v>
+        <v>122746097</v>
       </c>
       <c r="B23" t="n">
-        <v>78647</v>
+        <v>92296</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>1506</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stångsjömon, Ång</t>
+          <t>Åskojan NÖ, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668905</v>
+        <v>669744</v>
       </c>
       <c r="R23" t="n">
-        <v>7090825</v>
+        <v>7090762</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2833,12 +2805,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2853,57 +2825,61 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122745997</v>
+        <v>122746093</v>
       </c>
       <c r="B24" t="n">
-        <v>78739</v>
+        <v>92285</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>2062</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ång</t>
+          <t>Åskojan NÖ, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>669899</v>
+        <v>669741</v>
       </c>
       <c r="R24" t="n">
-        <v>7090587</v>
+        <v>7090741</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2955,21 +2931,21 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Jessica  Åström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122745985</v>
+        <v>67474872</v>
       </c>
       <c r="B25" t="n">
-        <v>92527</v>
+        <v>93189</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2997,14 +2973,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ång</t>
+          <t>Stångsjömon, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>669866</v>
+        <v>669710</v>
       </c>
       <c r="R25" t="n">
-        <v>7090641</v>
+        <v>7090503</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3031,12 +3007,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3051,26 +3027,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Sören Uppsäll, Per Nihlén</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122745980</v>
+        <v>67474652</v>
       </c>
       <c r="B26" t="n">
-        <v>90283</v>
+        <v>93197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3078,34 +3050,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långtjärnsberget SV, Ång</t>
+          <t>Stångsjömon, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>669891</v>
+        <v>669504</v>
       </c>
       <c r="R26" t="n">
-        <v>7090661</v>
+        <v>7090118</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3132,12 +3104,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3152,61 +3124,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Sören Uppsäll, Per Nihlén</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122745957</v>
+        <v>67474871</v>
       </c>
       <c r="B27" t="n">
-        <v>91210</v>
+        <v>93209</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>4366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Persbo NV, Ång</t>
+          <t>Stångsjömon, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>669995</v>
+        <v>669760</v>
       </c>
       <c r="R27" t="n">
-        <v>7090598</v>
+        <v>7090526</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3233,12 +3201,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3253,26 +3221,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Sören Uppsäll, Per Nihlén</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>67474868</v>
+        <v>67474876</v>
       </c>
       <c r="B28" t="n">
-        <v>92551</v>
+        <v>93209</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3280,21 +3244,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3304,10 +3268,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>669921</v>
+        <v>669426</v>
       </c>
       <c r="R28" t="n">
-        <v>7090665</v>
+        <v>7090382</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3366,10 +3330,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>67474657</v>
+        <v>122743253</v>
       </c>
       <c r="B29" t="n">
-        <v>90283</v>
+        <v>91934</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3377,34 +3341,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1962</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stångsjömon, Ång</t>
+          <t>Gräningen SÖ, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>669717</v>
+        <v>669770</v>
       </c>
       <c r="R29" t="n">
-        <v>7090048</v>
+        <v>7090696</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3431,12 +3395,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3451,44 +3415,48 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>67474866</v>
+        <v>67474653</v>
       </c>
       <c r="B30" t="n">
-        <v>92529</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3498,10 +3466,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>669881</v>
+        <v>669504</v>
       </c>
       <c r="R30" t="n">
-        <v>7090646</v>
+        <v>7090118</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3560,10 +3528,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>67474644</v>
+        <v>122743241</v>
       </c>
       <c r="B31" t="n">
-        <v>92529</v>
+        <v>83311</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3571,34 +3539,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stångsjömon, Ång</t>
+          <t>Gräningen Ö, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668905</v>
+        <v>669788</v>
       </c>
       <c r="R31" t="n">
-        <v>7090679</v>
+        <v>7090723</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3625,12 +3593,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3645,57 +3613,61 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122745921</v>
+        <v>67474874</v>
       </c>
       <c r="B32" t="n">
-        <v>90001</v>
+        <v>79084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6276</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ång</t>
+          <t>Stångsjömon, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>670017</v>
+        <v>669648</v>
       </c>
       <c r="R32" t="n">
-        <v>7090501</v>
+        <v>7090488</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3722,12 +3694,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3742,61 +3714,57 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Sören Uppsäll, Per Nihlén</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122745977</v>
+        <v>67474875</v>
       </c>
       <c r="B33" t="n">
-        <v>90001</v>
+        <v>79085</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6276</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Långtjärnsberget V, Ång</t>
+          <t>Stångsjömon, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>669893</v>
+        <v>669648</v>
       </c>
       <c r="R33" t="n">
-        <v>7090670</v>
+        <v>7090488</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3823,12 +3791,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3843,26 +3811,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Sören Uppsäll, Per Nihlén</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122745955</v>
+        <v>73354518</v>
       </c>
       <c r="B34" t="n">
-        <v>78738</v>
+        <v>79085</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3870,34 +3834,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Persbo NV, Ång</t>
+          <t>Stångsjömon, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>670064</v>
+        <v>669566</v>
       </c>
       <c r="R34" t="n">
-        <v>7090520</v>
+        <v>7090441</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3924,12 +3888,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3944,61 +3908,57 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Sören Uppsäll, Per Nihlén</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122745954</v>
+        <v>122746091</v>
       </c>
       <c r="B35" t="n">
-        <v>98361</v>
+        <v>92333</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6040186</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Persbo NV, Ång</t>
+          <t>Tretjärnarna V, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>670067</v>
+        <v>669737</v>
       </c>
       <c r="R35" t="n">
-        <v>7090528</v>
+        <v>7090747</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4050,56 +4010,56 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
+          <t>Jessica  Åström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122745992</v>
+        <v>67474862</v>
       </c>
       <c r="B36" t="n">
-        <v>90001</v>
+        <v>78993</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6276</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ång</t>
+          <t>Stångsjömon, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>669881</v>
+        <v>670001</v>
       </c>
       <c r="R36" t="n">
-        <v>7090639</v>
+        <v>7089924</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4126,12 +4086,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4146,26 +4106,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Sören Uppsäll, Per Nihlén</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122745931</v>
+        <v>73354519</v>
       </c>
       <c r="B37" t="n">
-        <v>79598</v>
+        <v>80298</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4173,34 +4129,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>388</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Persbo NV, Ång</t>
+          <t>Stångsjömon, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>670135</v>
+        <v>669972</v>
       </c>
       <c r="R37" t="n">
-        <v>7090325</v>
+        <v>7089998</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4227,12 +4183,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4241,67 +4197,64 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Sören Uppsäll, Per Nihlén</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122745956</v>
+        <v>67474863</v>
       </c>
       <c r="B38" t="n">
-        <v>78647</v>
+        <v>93213</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Persbo NV, Ång</t>
+          <t>Stångsjömon, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>669995</v>
+        <v>670109</v>
       </c>
       <c r="R38" t="n">
-        <v>7090580</v>
+        <v>7089941</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4328,12 +4281,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4348,26 +4301,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Sören Uppsäll, Per Nihlén</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122743247</v>
+        <v>67474860</v>
       </c>
       <c r="B39" t="n">
-        <v>91245</v>
+        <v>93197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4375,34 +4324,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gräningen Ö, Ång</t>
+          <t>Stångsjömon, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>669746</v>
+        <v>669896</v>
       </c>
       <c r="R39" t="n">
-        <v>7090734</v>
+        <v>7090075</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4429,12 +4378,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4449,48 +4398,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Sören Uppsäll, Per Nihlén</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>67474652</v>
+        <v>67474861</v>
       </c>
       <c r="B40" t="n">
-        <v>92535</v>
+        <v>93209</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4500,10 +4445,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>669504</v>
+        <v>669989</v>
       </c>
       <c r="R40" t="n">
-        <v>7090118</v>
+        <v>7089930</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4562,45 +4507,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>67474862</v>
+        <v>122745986</v>
       </c>
       <c r="B41" t="n">
-        <v>78647</v>
+        <v>92187</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stångsjömon, Ång</t>
+          <t>Tretjärnarna V, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>670001</v>
+        <v>669878</v>
       </c>
       <c r="R41" t="n">
-        <v>7089924</v>
+        <v>7090648</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4627,12 +4572,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4647,22 +4592,26 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
+          <t>Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122746002</v>
+        <v>122745956</v>
       </c>
       <c r="B42" t="n">
-        <v>92527</v>
+        <v>78995</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4670,34 +4619,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ång</t>
+          <t>Persbo NV, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>669880</v>
+        <v>669995</v>
       </c>
       <c r="R42" t="n">
-        <v>7090558</v>
+        <v>7090580</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4749,21 +4698,21 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122745935</v>
+        <v>122745988</v>
       </c>
       <c r="B43" t="n">
-        <v>92529</v>
+        <v>78995</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4771,34 +4720,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Persbo NV, Ång</t>
+          <t>Tretjärnarna V, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>670140</v>
+        <v>669915</v>
       </c>
       <c r="R43" t="n">
-        <v>7090259</v>
+        <v>7090620</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4850,43 +4799,43 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Jessica  Åström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122745922</v>
+        <v>122745771</v>
       </c>
       <c r="B44" t="n">
-        <v>92527</v>
+        <v>92087</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4361</v>
+        <v>1503</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4896,10 +4845,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>670033</v>
+        <v>669915</v>
       </c>
       <c r="R44" t="n">
-        <v>7090453</v>
+        <v>7090653</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4926,12 +4875,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4951,21 +4900,21 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>67474877</v>
+        <v>122745772</v>
       </c>
       <c r="B45" t="n">
-        <v>92529</v>
+        <v>90936</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4973,34 +4922,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stångsjömon, Ång</t>
+          <t>Renskinns- NV, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>669299</v>
+        <v>669892</v>
       </c>
       <c r="R45" t="n">
-        <v>7090047</v>
+        <v>7090638</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5027,12 +4976,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5047,22 +4996,26 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>67474650</v>
+        <v>122745942</v>
       </c>
       <c r="B46" t="n">
-        <v>78980</v>
+        <v>90936</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5070,34 +5023,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stångsjömon, Ång</t>
+          <t>Persbo NV, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668972</v>
+        <v>670130</v>
       </c>
       <c r="R46" t="n">
-        <v>7090806</v>
+        <v>7090306</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5124,12 +5077,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5144,22 +5097,26 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122745968</v>
+        <v>122745980</v>
       </c>
       <c r="B47" t="n">
-        <v>5492</v>
+        <v>90936</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5167,34 +5124,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>101410</v>
+        <v>1962</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Ång</t>
+          <t>Långtjärnsberget SV, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>669955</v>
+        <v>669891</v>
       </c>
       <c r="R47" t="n">
-        <v>7090535</v>
+        <v>7090661</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5246,56 +5203,56 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122746000</v>
+        <v>67474868</v>
       </c>
       <c r="B48" t="n">
-        <v>92152</v>
+        <v>93213</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4745</v>
+        <v>2059</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ång</t>
+          <t>Stångsjömon, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>669882</v>
+        <v>669921</v>
       </c>
       <c r="R48" t="n">
-        <v>7090561</v>
+        <v>7090665</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5322,12 +5279,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5342,61 +5299,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Sören Uppsäll, Per Nihlén</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122745961</v>
+        <v>67474869</v>
       </c>
       <c r="B49" t="n">
-        <v>92152</v>
+        <v>93213</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4745</v>
+        <v>2059</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ång</t>
+          <t>Stångsjömon, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>669966</v>
+        <v>669907</v>
       </c>
       <c r="R49" t="n">
-        <v>7090624</v>
+        <v>7090588</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5423,12 +5376,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5443,61 +5396,57 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Sören Uppsäll, Per Nihlén</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>67474645</v>
+        <v>122745769</v>
       </c>
       <c r="B50" t="n">
-        <v>92535</v>
+        <v>93217</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stångsjömon, Ång</t>
+          <t>Renskinns- V, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668922</v>
+        <v>669933</v>
       </c>
       <c r="R50" t="n">
-        <v>7090748</v>
+        <v>7090655</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5524,12 +5473,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5544,57 +5493,61 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>67474875</v>
+        <v>122745919</v>
       </c>
       <c r="B51" t="n">
-        <v>78739</v>
+        <v>93217</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stångsjömon, Ång</t>
+          <t>Renskinns- V, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>669648</v>
+        <v>669947</v>
       </c>
       <c r="R51" t="n">
-        <v>7090488</v>
+        <v>7090550</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5621,12 +5574,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5641,57 +5594,61 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122745986</v>
+        <v>122745940</v>
       </c>
       <c r="B52" t="n">
-        <v>91506</v>
+        <v>91966</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>65</v>
+        <v>2079</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ång</t>
+          <t>Renskinns- V, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>669878</v>
+        <v>670126</v>
       </c>
       <c r="R52" t="n">
-        <v>7090648</v>
+        <v>7090300</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5743,56 +5700,56 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
+          <t>Jessica  Åström</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122746093</v>
+        <v>122745971</v>
       </c>
       <c r="B53" t="n">
-        <v>91603</v>
+        <v>91966</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2062</v>
+        <v>2079</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Åskojan NÖ, Ång</t>
+          <t>Renskinns- NV, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>669741</v>
+        <v>669936</v>
       </c>
       <c r="R53" t="n">
-        <v>7090741</v>
+        <v>7090682</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5844,56 +5801,56 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
+          <t>Jessica  Åström</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>67474860</v>
+        <v>122745999</v>
       </c>
       <c r="B54" t="n">
-        <v>92535</v>
+        <v>91966</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stångsjömon, Ång</t>
+          <t>Tretjärnarna V, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>669896</v>
+        <v>669873</v>
       </c>
       <c r="R54" t="n">
-        <v>7090075</v>
+        <v>7090572</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5920,12 +5877,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5940,22 +5897,26 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
+          <t>Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>73354518</v>
+        <v>122745918</v>
       </c>
       <c r="B55" t="n">
-        <v>78739</v>
+        <v>93226</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5963,34 +5924,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>3100</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stångsjömon, Ång</t>
+          <t>Renskinns- V, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>669566</v>
+        <v>669897</v>
       </c>
       <c r="R55" t="n">
-        <v>7090441</v>
+        <v>7090549</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6017,12 +5978,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6037,22 +5998,26 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122743240</v>
+        <v>67474867</v>
       </c>
       <c r="B56" t="n">
-        <v>78647</v>
+        <v>93189</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6060,34 +6025,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gräningen Ö, Ång</t>
+          <t>Stångsjömon, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>669806</v>
+        <v>669891</v>
       </c>
       <c r="R56" t="n">
-        <v>7090755</v>
+        <v>7090656</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6114,12 +6079,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6134,26 +6099,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Sören Uppsäll, Per Nihlén</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>67474867</v>
+        <v>122745922</v>
       </c>
       <c r="B57" t="n">
-        <v>92527</v>
+        <v>93193</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6181,14 +6142,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stångsjömon, Ång</t>
+          <t>Renskinns- V, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>669891</v>
+        <v>670033</v>
       </c>
       <c r="R57" t="n">
-        <v>7090656</v>
+        <v>7090453</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6215,12 +6176,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6235,57 +6196,61 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>67474865</v>
+        <v>122745938</v>
       </c>
       <c r="B58" t="n">
-        <v>90001</v>
+        <v>93193</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stångsjömon, Ång</t>
+          <t>Renskinns- V, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>669866</v>
+        <v>670115</v>
       </c>
       <c r="R58" t="n">
-        <v>7090604</v>
+        <v>7090257</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6312,12 +6277,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6332,22 +6297,26 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
+          <t>Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122745982</v>
+        <v>122745939</v>
       </c>
       <c r="B59" t="n">
-        <v>92527</v>
+        <v>93193</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6375,14 +6344,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ång</t>
+          <t>Djuptjärnen NV, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>669878</v>
+        <v>670132</v>
       </c>
       <c r="R59" t="n">
-        <v>7090653</v>
+        <v>7090279</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6434,21 +6403,21 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Jessica  Åström</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122745938</v>
+        <v>122745959</v>
       </c>
       <c r="B60" t="n">
-        <v>92527</v>
+        <v>93193</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6480,10 +6449,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>670115</v>
+        <v>670125</v>
       </c>
       <c r="R60" t="n">
-        <v>7090257</v>
+        <v>7090225</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6535,21 +6504,21 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122745958</v>
+        <v>122745963</v>
       </c>
       <c r="B61" t="n">
-        <v>5492</v>
+        <v>93193</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6557,21 +6526,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>101410</v>
+        <v>4361</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6581,10 +6550,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>670106</v>
+        <v>669940</v>
       </c>
       <c r="R61" t="n">
-        <v>7090266</v>
+        <v>7090640</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6636,21 +6605,21 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Jessica  Åström</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>67474654</v>
+        <v>122745966</v>
       </c>
       <c r="B62" t="n">
-        <v>91265</v>
+        <v>93193</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6658,34 +6627,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5442</v>
+        <v>4361</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stångsjömon, Ång</t>
+          <t>Storlandsberget N, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>669608</v>
+        <v>670035</v>
       </c>
       <c r="R62" t="n">
-        <v>7090080</v>
+        <v>7090454</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6712,12 +6681,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6732,22 +6701,26 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>67474864</v>
+        <v>122745975</v>
       </c>
       <c r="B63" t="n">
-        <v>92529</v>
+        <v>93193</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6755,34 +6728,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Stångsjömon, Ång</t>
+          <t>Renskinns- NV, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>669866</v>
+        <v>669892</v>
       </c>
       <c r="R63" t="n">
-        <v>7090604</v>
+        <v>7090677</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6809,12 +6782,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6829,22 +6802,26 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122745919</v>
+        <v>122745981</v>
       </c>
       <c r="B64" t="n">
-        <v>92551</v>
+        <v>93193</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6852,34 +6829,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ång</t>
+          <t>Tretjärnarna V, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>669947</v>
+        <v>670035</v>
       </c>
       <c r="R64" t="n">
-        <v>7090550</v>
+        <v>7090545</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6931,56 +6908,56 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122745960</v>
+        <v>122745982</v>
       </c>
       <c r="B65" t="n">
-        <v>92535</v>
+        <v>93193</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ång</t>
+          <t>Tretjärnarna V, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>670120</v>
+        <v>669878</v>
       </c>
       <c r="R65" t="n">
-        <v>7090287</v>
+        <v>7090653</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7032,21 +7009,21 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122745918</v>
+        <v>122745985</v>
       </c>
       <c r="B66" t="n">
-        <v>92560</v>
+        <v>93193</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7054,34 +7031,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ång</t>
+          <t>Tretjärnarna V, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>669897</v>
+        <v>669866</v>
       </c>
       <c r="R66" t="n">
-        <v>7090549</v>
+        <v>7090641</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7133,21 +7110,21 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Jessica  Åström</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122745976</v>
+        <v>122745989</v>
       </c>
       <c r="B67" t="n">
-        <v>92529</v>
+        <v>93193</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7155,34 +7132,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Abborrtj. Ö, Ång</t>
+          <t>Tretjärnarna V, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>669891</v>
+        <v>669893</v>
       </c>
       <c r="R67" t="n">
-        <v>7090673</v>
+        <v>7090649</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7234,56 +7211,56 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122745941</v>
+        <v>122745991</v>
       </c>
       <c r="B68" t="n">
-        <v>92519</v>
+        <v>93193</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6055</v>
+        <v>4361</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ång</t>
+          <t>Tretjärnarna V, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>670135</v>
+        <v>669879</v>
       </c>
       <c r="R68" t="n">
-        <v>7090325</v>
+        <v>7090606</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7335,21 +7312,21 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Jessica  Åström</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122743241</v>
+        <v>122746002</v>
       </c>
       <c r="B69" t="n">
-        <v>75075</v>
+        <v>93193</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7357,34 +7334,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>4361</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Gräningen Ö, Ång</t>
+          <t>Tretjärnarna V, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>669788</v>
+        <v>669880</v>
       </c>
       <c r="R69" t="n">
-        <v>7090723</v>
+        <v>7090558</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7411,12 +7388,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7436,21 +7413,21 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
+          <t>Jessica  Åström</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122745988</v>
+        <v>67474864</v>
       </c>
       <c r="B70" t="n">
-        <v>78647</v>
+        <v>93191</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7458,34 +7435,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ång</t>
+          <t>Stångsjömon, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>669915</v>
+        <v>669866</v>
       </c>
       <c r="R70" t="n">
-        <v>7090620</v>
+        <v>7090604</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7512,12 +7489,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7532,26 +7509,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Sören Uppsäll, Per Nihlén</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>67474869</v>
+        <v>67474866</v>
       </c>
       <c r="B71" t="n">
-        <v>92551</v>
+        <v>93191</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7559,21 +7532,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7583,10 +7556,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>669907</v>
+        <v>669881</v>
       </c>
       <c r="R71" t="n">
-        <v>7090588</v>
+        <v>7090646</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7645,45 +7618,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>67474871</v>
+        <v>122745935</v>
       </c>
       <c r="B72" t="n">
-        <v>92547</v>
+        <v>93195</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Stångsjömon, Ång</t>
+          <t>Persbo NV, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>669760</v>
+        <v>670140</v>
       </c>
       <c r="R72" t="n">
-        <v>7090526</v>
+        <v>7090259</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7710,12 +7683,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7730,22 +7703,26 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>67474647</v>
+        <v>122745976</v>
       </c>
       <c r="B73" t="n">
-        <v>78647</v>
+        <v>93195</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7753,34 +7730,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Stångsjömon, Ång</t>
+          <t>Abborrtj. Ö, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>668937</v>
+        <v>669891</v>
       </c>
       <c r="R73" t="n">
-        <v>7090808</v>
+        <v>7090673</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7807,12 +7784,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7827,22 +7804,26 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122745769</v>
+        <v>122745960</v>
       </c>
       <c r="B74" t="n">
-        <v>92551</v>
+        <v>93201</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7850,21 +7831,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7874,10 +7855,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>669933</v>
+        <v>670120</v>
       </c>
       <c r="R74" t="n">
-        <v>7090655</v>
+        <v>7090287</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7904,12 +7885,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7929,21 +7910,21 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122745939</v>
+        <v>122745994</v>
       </c>
       <c r="B75" t="n">
-        <v>92527</v>
+        <v>93201</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7951,34 +7932,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Djuptjärnen NV, Ång</t>
+          <t>Tretjärnarna V, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>670132</v>
+        <v>669879</v>
       </c>
       <c r="R75" t="n">
-        <v>7090279</v>
+        <v>7090603</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8030,43 +8011,43 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
+          <t>Jessica  Åström</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122745940</v>
+        <v>122745964</v>
       </c>
       <c r="B76" t="n">
-        <v>92727</v>
+        <v>93205</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2079</v>
+        <v>4365</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8076,10 +8057,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>670126</v>
+        <v>669924</v>
       </c>
       <c r="R76" t="n">
-        <v>7090300</v>
+        <v>7090647</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8131,56 +8112,56 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
+          <t>Jessica  Åström</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122746100</v>
+        <v>122745972</v>
       </c>
       <c r="B77" t="n">
-        <v>91241</v>
+        <v>93205</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1108</v>
+        <v>4365</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Åskojan SÖ, Ång</t>
+          <t>Renskinns- NV, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>669761</v>
+        <v>669935</v>
       </c>
       <c r="R77" t="n">
-        <v>7090742</v>
+        <v>7090680</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8232,43 +8213,43 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
+          <t>Jessica  Åström</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122745771</v>
+        <v>122745961</v>
       </c>
       <c r="B78" t="n">
-        <v>91406</v>
+        <v>92845</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1503</v>
+        <v>4745</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8278,10 +8259,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>669915</v>
+        <v>669966</v>
       </c>
       <c r="R78" t="n">
-        <v>7090653</v>
+        <v>7090624</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8308,12 +8289,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8333,21 +8314,21 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Jessica  Åström</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122745934</v>
+        <v>122746000</v>
       </c>
       <c r="B79" t="n">
-        <v>78738</v>
+        <v>92845</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8355,34 +8336,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>4745</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ång</t>
+          <t>Tretjärnarna V, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>670107</v>
+        <v>669882</v>
       </c>
       <c r="R79" t="n">
-        <v>7090350</v>
+        <v>7090561</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8434,56 +8415,56 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
+          <t>Jessica  Åström</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>67474651</v>
+        <v>122745957</v>
       </c>
       <c r="B80" t="n">
-        <v>78647</v>
+        <v>91876</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Stångsjömon, Ång</t>
+          <t>Persbo NV, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>668977</v>
+        <v>669995</v>
       </c>
       <c r="R80" t="n">
-        <v>7090760</v>
+        <v>7090598</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8510,12 +8491,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8530,46 +8511,46 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
+          <t>Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122745995</v>
+        <v>122746003</v>
       </c>
       <c r="B81" t="n">
-        <v>78386</v>
+        <v>93230</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6437</v>
+        <v>5449</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -8577,10 +8558,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>669889</v>
+        <v>669867</v>
       </c>
       <c r="R81" t="n">
-        <v>7090578</v>
+        <v>7090564</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8632,56 +8613,59 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Jessica  Åström</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122745927</v>
+        <v>122745941</v>
       </c>
       <c r="B82" t="n">
-        <v>79569</v>
+        <v>93181</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>6055</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Renskinns- V, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>670109</v>
+        <v>670135</v>
       </c>
       <c r="R82" t="n">
-        <v>7090398</v>
+        <v>7090325</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8722,6 +8706,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8733,21 +8718,21 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122743245</v>
+        <v>67474865</v>
       </c>
       <c r="B83" t="n">
-        <v>91699</v>
+        <v>90691</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8755,34 +8740,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1209</v>
+        <v>6276</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Gräningen Ö, Ång</t>
+          <t>Stångsjömon, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>669764</v>
+        <v>669866</v>
       </c>
       <c r="R83" t="n">
-        <v>7090736</v>
+        <v>7090604</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8809,12 +8794,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2017-09-07</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8829,26 +8814,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Sören Uppsäll, Per Nihlén</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122745964</v>
+        <v>122745921</v>
       </c>
       <c r="B84" t="n">
-        <v>92539</v>
+        <v>90695</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8856,21 +8837,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4365</v>
+        <v>6276</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8880,10 +8861,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>669924</v>
+        <v>670017</v>
       </c>
       <c r="R84" t="n">
-        <v>7090647</v>
+        <v>7090501</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8935,56 +8916,56 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
+          <t>Jessica  Åström</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122745963</v>
+        <v>122745977</v>
       </c>
       <c r="B85" t="n">
-        <v>92527</v>
+        <v>90695</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ång</t>
+          <t>Långtjärnsberget V, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>669940</v>
+        <v>669893</v>
       </c>
       <c r="R85" t="n">
-        <v>7090640</v>
+        <v>7090670</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9036,56 +9017,56 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>67474649</v>
+        <v>122745983</v>
       </c>
       <c r="B86" t="n">
-        <v>92535</v>
+        <v>90695</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Stångsjömon, Ång</t>
+          <t>Tretjärnarna V, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>668949</v>
+        <v>669877</v>
       </c>
       <c r="R86" t="n">
-        <v>7090807</v>
+        <v>7090654</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9112,12 +9093,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9132,22 +9113,26 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122745993</v>
+        <v>122745984</v>
       </c>
       <c r="B87" t="n">
-        <v>90001</v>
+        <v>90695</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9175,14 +9160,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ång</t>
+          <t>Skalberget NV, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>669877</v>
+        <v>669871</v>
       </c>
       <c r="R87" t="n">
-        <v>7090603</v>
+        <v>7090650</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9234,56 +9219,56 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
+          <t>Jessica  Åström</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122745920</v>
+        <v>122745992</v>
       </c>
       <c r="B88" t="n">
-        <v>105383</v>
+        <v>90695</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>224098</v>
+        <v>6276</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Renskinns- V, Ång</t>
+          <t>Tretjärnarna V, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>669984</v>
+        <v>669881</v>
       </c>
       <c r="R88" t="n">
-        <v>7090520</v>
+        <v>7090639</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9335,56 +9320,56 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>73354519</v>
+        <v>122745993</v>
       </c>
       <c r="B89" t="n">
-        <v>79949</v>
+        <v>90695</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>388</v>
+        <v>6276</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Stångsjömon, Ång</t>
+          <t>Tretjärnarna V, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>669972</v>
+        <v>669877</v>
       </c>
       <c r="R89" t="n">
-        <v>7089998</v>
+        <v>7090603</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9411,12 +9396,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9425,29 +9410,32 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
+          <t>Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>67474655</v>
+        <v>122745995</v>
       </c>
       <c r="B90" t="n">
-        <v>78738</v>
+        <v>78732</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9455,34 +9443,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stångsjömon, Ång</t>
+          <t>Tretjärnarna V, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>669647</v>
+        <v>669889</v>
       </c>
       <c r="R90" t="n">
-        <v>7090068</v>
+        <v>7090578</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9509,12 +9497,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9529,22 +9517,26 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>67474653</v>
+        <v>122745934</v>
       </c>
       <c r="B91" t="n">
-        <v>78980</v>
+        <v>79086</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9552,34 +9544,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Stångsjömon, Ång</t>
+          <t>Renskinns- V, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>669504</v>
+        <v>670107</v>
       </c>
       <c r="R91" t="n">
-        <v>7090118</v>
+        <v>7090350</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9606,12 +9598,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9626,22 +9618,26 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
+          <t>Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122745942</v>
+        <v>122745955</v>
       </c>
       <c r="B92" t="n">
-        <v>90283</v>
+        <v>79086</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9649,21 +9645,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9673,10 +9669,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>670130</v>
+        <v>670064</v>
       </c>
       <c r="R92" t="n">
-        <v>7090306</v>
+        <v>7090520</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9728,56 +9724,56 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
+          <t>Jessica  Åström</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122745984</v>
+        <v>122745931</v>
       </c>
       <c r="B93" t="n">
-        <v>90001</v>
+        <v>79948</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6276</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Skalberget NV, Ång</t>
+          <t>Persbo NV, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>669871</v>
+        <v>670135</v>
       </c>
       <c r="R93" t="n">
-        <v>7090650</v>
+        <v>7090325</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9829,56 +9825,56 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Helene Andersson, Jessica  Åström</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122745983</v>
+        <v>122745958</v>
       </c>
       <c r="B94" t="n">
-        <v>90001</v>
+        <v>5495</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6276</v>
+        <v>101410</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Ång</t>
+          <t>Renskinns- V, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>669877</v>
+        <v>670106</v>
       </c>
       <c r="R94" t="n">
-        <v>7090654</v>
+        <v>7090266</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9930,56 +9926,56 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>67474861</v>
+        <v>122745968</v>
       </c>
       <c r="B95" t="n">
-        <v>92547</v>
+        <v>5495</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4366</v>
+        <v>101410</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Stångsjömon, Ång</t>
+          <t>Renskinns- NV, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>669989</v>
+        <v>669955</v>
       </c>
       <c r="R95" t="n">
-        <v>7089930</v>
+        <v>7090535</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10006,12 +10002,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2017-09-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10026,15 +10022,428 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>122745954</v>
+      </c>
+      <c r="B96" t="n">
+        <v>99122</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Persbo NV, Ång</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>670067</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7090528</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>122745920</v>
+      </c>
+      <c r="B97" t="n">
+        <v>106235</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>224098</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Kalktallört</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Renskinns- V, Ång</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>669984</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7090520</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>122745997</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Tretjärnarna V, Ång</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>669899</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7090587</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>122745927</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79919</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Renskinns- V, Ång</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>670109</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7090398</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Tyfallsjön artfynd.xlsx
+++ b/artfynd/Tyfallsjön artfynd.xlsx
@@ -2036,7 +2036,7 @@
         <v>122743240</v>
       </c>
       <c r="B16" t="n">
-        <v>78995</v>
+        <v>79039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>122743248</v>
       </c>
       <c r="B17" t="n">
-        <v>92212</v>
+        <v>92245</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>122746094</v>
       </c>
       <c r="B18" t="n">
-        <v>92212</v>
+        <v>92245</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>122746100</v>
       </c>
       <c r="B19" t="n">
-        <v>91909</v>
+        <v>91970</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>122743247</v>
       </c>
       <c r="B20" t="n">
-        <v>91913</v>
+        <v>91974</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>122746092</v>
       </c>
       <c r="B21" t="n">
-        <v>91913</v>
+        <v>91974</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>122743245</v>
       </c>
       <c r="B22" t="n">
-        <v>92373</v>
+        <v>92406</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>122746097</v>
       </c>
       <c r="B23" t="n">
-        <v>92296</v>
+        <v>92329</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>122746093</v>
       </c>
       <c r="B24" t="n">
-        <v>92285</v>
+        <v>92318</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>122743253</v>
       </c>
       <c r="B29" t="n">
-        <v>91934</v>
+        <v>91995</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>122743241</v>
       </c>
       <c r="B31" t="n">
-        <v>83311</v>
+        <v>83358</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>122746091</v>
       </c>
       <c r="B35" t="n">
-        <v>92333</v>
+        <v>92366</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>122745986</v>
       </c>
       <c r="B41" t="n">
-        <v>92187</v>
+        <v>92220</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>122745956</v>
       </c>
       <c r="B42" t="n">
-        <v>78995</v>
+        <v>79039</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>122745988</v>
       </c>
       <c r="B43" t="n">
-        <v>78995</v>
+        <v>79039</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>122745771</v>
       </c>
       <c r="B44" t="n">
-        <v>92087</v>
+        <v>92153</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>122745772</v>
       </c>
       <c r="B45" t="n">
-        <v>90936</v>
+        <v>90997</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>122745942</v>
       </c>
       <c r="B46" t="n">
-        <v>90936</v>
+        <v>90997</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>122745980</v>
       </c>
       <c r="B47" t="n">
-        <v>90936</v>
+        <v>90997</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>122745769</v>
       </c>
       <c r="B50" t="n">
-        <v>93217</v>
+        <v>93287</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>122745919</v>
       </c>
       <c r="B51" t="n">
-        <v>93217</v>
+        <v>93287</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>122745940</v>
       </c>
       <c r="B52" t="n">
-        <v>91966</v>
+        <v>92027</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>122745971</v>
       </c>
       <c r="B53" t="n">
-        <v>91966</v>
+        <v>92027</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>122745999</v>
       </c>
       <c r="B54" t="n">
-        <v>91966</v>
+        <v>92027</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>122745918</v>
       </c>
       <c r="B55" t="n">
-        <v>93226</v>
+        <v>93296</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>122745922</v>
       </c>
       <c r="B57" t="n">
-        <v>93193</v>
+        <v>93263</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>122745938</v>
       </c>
       <c r="B58" t="n">
-        <v>93193</v>
+        <v>93263</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         <v>122745939</v>
       </c>
       <c r="B59" t="n">
-        <v>93193</v>
+        <v>93263</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>122745959</v>
       </c>
       <c r="B60" t="n">
-        <v>93193</v>
+        <v>93263</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>122745963</v>
       </c>
       <c r="B61" t="n">
-        <v>93193</v>
+        <v>93263</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>122745966</v>
       </c>
       <c r="B62" t="n">
-        <v>93193</v>
+        <v>93263</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         <v>122745975</v>
       </c>
       <c r="B63" t="n">
-        <v>93193</v>
+        <v>93263</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>122745981</v>
       </c>
       <c r="B64" t="n">
-        <v>93193</v>
+        <v>93263</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>122745982</v>
       </c>
       <c r="B65" t="n">
-        <v>93193</v>
+        <v>93263</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>122745985</v>
       </c>
       <c r="B66" t="n">
-        <v>93193</v>
+        <v>93263</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>122745989</v>
       </c>
       <c r="B67" t="n">
-        <v>93193</v>
+        <v>93263</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>122745991</v>
       </c>
       <c r="B68" t="n">
-        <v>93193</v>
+        <v>93263</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>122746002</v>
       </c>
       <c r="B69" t="n">
-        <v>93193</v>
+        <v>93263</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>122745935</v>
       </c>
       <c r="B72" t="n">
-        <v>93195</v>
+        <v>93265</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>122745976</v>
       </c>
       <c r="B73" t="n">
-        <v>93195</v>
+        <v>93265</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         <v>122745960</v>
       </c>
       <c r="B74" t="n">
-        <v>93201</v>
+        <v>93271</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>122745994</v>
       </c>
       <c r="B75" t="n">
-        <v>93201</v>
+        <v>93271</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>122745964</v>
       </c>
       <c r="B76" t="n">
-        <v>93205</v>
+        <v>93275</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>122745972</v>
       </c>
       <c r="B77" t="n">
-        <v>93205</v>
+        <v>93275</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>122745961</v>
       </c>
       <c r="B78" t="n">
-        <v>92845</v>
+        <v>92915</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         <v>122746000</v>
       </c>
       <c r="B79" t="n">
-        <v>92845</v>
+        <v>92915</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>122745957</v>
       </c>
       <c r="B80" t="n">
-        <v>91876</v>
+        <v>91937</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>122746003</v>
       </c>
       <c r="B81" t="n">
-        <v>93230</v>
+        <v>93300</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>122745941</v>
       </c>
       <c r="B82" t="n">
-        <v>93181</v>
+        <v>93255</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>122745921</v>
       </c>
       <c r="B84" t="n">
-        <v>90695</v>
+        <v>90756</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>122745977</v>
       </c>
       <c r="B85" t="n">
-        <v>90695</v>
+        <v>90756</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>122745983</v>
       </c>
       <c r="B86" t="n">
-        <v>90695</v>
+        <v>90756</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>122745984</v>
       </c>
       <c r="B87" t="n">
-        <v>90695</v>
+        <v>90756</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>122745992</v>
       </c>
       <c r="B88" t="n">
-        <v>90695</v>
+        <v>90756</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>122745993</v>
       </c>
       <c r="B89" t="n">
-        <v>90695</v>
+        <v>90756</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>122745995</v>
       </c>
       <c r="B90" t="n">
-        <v>78732</v>
+        <v>78776</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>122745934</v>
       </c>
       <c r="B91" t="n">
-        <v>79086</v>
+        <v>79130</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>122745955</v>
       </c>
       <c r="B92" t="n">
-        <v>79086</v>
+        <v>79130</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>122745931</v>
       </c>
       <c r="B93" t="n">
-        <v>79948</v>
+        <v>79992</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>122745958</v>
       </c>
       <c r="B94" t="n">
-        <v>5495</v>
+        <v>5497</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         <v>122745968</v>
       </c>
       <c r="B95" t="n">
-        <v>5495</v>
+        <v>5497</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>122745954</v>
       </c>
       <c r="B96" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>122745920</v>
       </c>
       <c r="B97" t="n">
-        <v>106235</v>
+        <v>106311</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>122745997</v>
       </c>
       <c r="B98" t="n">
-        <v>79087</v>
+        <v>79131</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10349,7 +10349,7 @@
         <v>122745927</v>
       </c>
       <c r="B99" t="n">
-        <v>79919</v>
+        <v>79963</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
